--- a/Docs/QA-Testing/Test_Case_Report_API.xlsx
+++ b/Docs/QA-Testing/Test_Case_Report_API.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\MouseWithoutBorders\moi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\MouseWithoutBorders\repo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B62688D-1C17-4269-9429-2D87234E469C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46F7D557-EEB6-4240-A06D-B3F37E6872AF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="0" windowWidth="11715" windowHeight="12330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Docs/QA-Testing/Test_Case_Report_API.xlsx
+++ b/Docs/QA-Testing/Test_Case_Report_API.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\MouseWithoutBorders\repo\moi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\Online-Store-sprint-4 (1)\Online-Store-sprint-4\Docs\QA-Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F9009F1-6294-4617-88D9-54B8895A7554}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68816755-4B48-4825-B38F-72ACC9445B5E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10200" windowHeight="7560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="165">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -367,51 +367,6 @@
     <t>Complete order (Customer)</t>
   </si>
   <si>
-    <t>BVA</t>
-  </si>
-  <si>
-    <t>TC-BVA-01</t>
-  </si>
-  <si>
-    <t>Register - Password = 12</t>
-  </si>
-  <si>
-    <t>TC-BVA-02</t>
-  </si>
-  <si>
-    <t>Register - Password = 123</t>
-  </si>
-  <si>
-    <t>TC-BVA-03</t>
-  </si>
-  <si>
-    <t>Add Cart - Quantity = 0</t>
-  </si>
-  <si>
-    <t>TC-BVA-04</t>
-  </si>
-  <si>
-    <t>Add Cart - Quantity = 1</t>
-  </si>
-  <si>
-    <t>TC-BVA-05</t>
-  </si>
-  <si>
-    <t>Add Product - Stock = 0</t>
-  </si>
-  <si>
-    <t>TC-BVA-06</t>
-  </si>
-  <si>
-    <t>Add Product - Stock = -1</t>
-  </si>
-  <si>
-    <t>TC-BVA-07</t>
-  </si>
-  <si>
-    <t>Add Product - Price = -1</t>
-  </si>
-  <si>
     <t>1. POST /login với username/password hợp lệ.</t>
   </si>
   <si>
@@ -523,45 +478,9 @@
     <t>1. PATCH /order/cancel/{id} đơn hàng người khác.</t>
   </si>
   <si>
-    <t>1. POST /register với pass độ dài 2.</t>
-  </si>
-  <si>
-    <t>1. POST /register với pass độ dài 3.</t>
-  </si>
-  <si>
-    <t>1. POST /cart/add với số lượng = 0.</t>
-  </si>
-  <si>
-    <t>1. POST /cart/add với số lượng = 1.</t>
-  </si>
-  <si>
-    <t>1. POST /seller/product/new với stock = 0.</t>
-  </si>
-  <si>
-    <t>1. POST /seller/product/new với stock = -1.</t>
-  </si>
-  <si>
-    <t>1. POST /seller/product/new với price = -1.</t>
-  </si>
-  <si>
     <t>SCRUM-46</t>
   </si>
   <si>
-    <t>SCRUM-47</t>
-  </si>
-  <si>
-    <t>SCRUM-48</t>
-  </si>
-  <si>
-    <t>SCRUM-49</t>
-  </si>
-  <si>
-    <t>SCRUM-50</t>
-  </si>
-  <si>
-    <t>SCRUM-51</t>
-  </si>
-  <si>
     <t>Kết quả (Newman lần đầu)</t>
   </si>
   <si>
@@ -578,21 +497,6 @@
   </si>
   <si>
     <t>Expected response to have status code 400 but got 500</t>
-  </si>
-  <si>
-    <t>Expected response to have status code 400 but got 200</t>
-  </si>
-  <si>
-    <t>Expected response to have status code 200 but got 500
-Expected 500 to deeply equal 200</t>
-  </si>
-  <si>
-    <t>Expected response to have status code 400 but got 500
-Expected 500 to deeply equal 400</t>
-  </si>
-  <si>
-    <t>Expected response to have status code 400 but got 200
-Expected 200 to deeply equal 400</t>
   </si>
   <si>
     <t>SECURITY</t>
@@ -617,7 +521,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -667,11 +571,6 @@
       <b/>
       <sz val="12"/>
       <color rgb="FF1F1F1F"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -736,7 +635,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -792,12 +691,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
@@ -807,7 +700,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1118,7 +1011,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A99EB60-1787-4B02-8F08-DF5C4102B1D2}">
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.85546875" customWidth="1"/>
@@ -1149,16 +1042,16 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>183</v>
+        <v>156</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>184</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
@@ -1185,13 +1078,13 @@
         <v>9</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>10</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G3" s="11"/>
       <c r="H3" s="12"/>
@@ -1208,13 +1101,13 @@
         <v>14</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>10</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="12"/>
@@ -1231,13 +1124,13 @@
         <v>17</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>10</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="12"/>
@@ -1254,13 +1147,13 @@
         <v>20</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>10</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G6" s="11"/>
       <c r="H6" s="12"/>
@@ -1277,13 +1170,13 @@
         <v>23</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G7" s="11"/>
       <c r="H7" s="12"/>
@@ -1300,13 +1193,13 @@
         <v>27</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>28</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="12"/>
@@ -1323,13 +1216,13 @@
         <v>27</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>31</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="12"/>
@@ -1346,13 +1239,13 @@
         <v>34</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>35</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G10" s="11"/>
       <c r="H10" s="12"/>
@@ -1369,13 +1262,13 @@
         <v>27</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>38</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G11" s="11"/>
       <c r="H11" s="12"/>
@@ -1392,13 +1285,13 @@
         <v>27</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>38</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G12" s="11"/>
       <c r="H12" s="12"/>
@@ -1415,13 +1308,13 @@
         <v>42</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>43</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G13" s="11"/>
       <c r="H13" s="12"/>
@@ -1451,13 +1344,13 @@
         <v>34</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G15" s="11"/>
       <c r="H15" s="12"/>
@@ -1474,13 +1367,13 @@
         <v>50</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G16" s="11"/>
       <c r="H16" s="12"/>
@@ -1497,13 +1390,13 @@
         <v>34</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G17" s="11"/>
       <c r="H17" s="12"/>
@@ -1520,13 +1413,13 @@
         <v>55</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G18" s="11"/>
       <c r="H18" s="12"/>
@@ -1543,13 +1436,13 @@
         <v>58</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G19" s="11"/>
       <c r="H19" s="12"/>
@@ -1566,13 +1459,13 @@
         <v>55</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G20" s="11"/>
       <c r="H20" s="12"/>
@@ -1589,13 +1482,13 @@
         <v>58</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>63</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G21" s="11"/>
       <c r="H21" s="12"/>
@@ -1612,20 +1505,20 @@
         <v>55</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>38</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>182</v>
+        <v>155</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="H22" s="12"/>
       <c r="I22" s="20" t="s">
-        <v>185</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
@@ -1639,13 +1532,13 @@
         <v>58</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>63</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G23" s="11"/>
       <c r="H23" s="12"/>
@@ -1662,13 +1555,13 @@
         <v>27</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>63</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G24" s="11"/>
       <c r="H24" s="12"/>
@@ -1698,13 +1591,13 @@
         <v>27</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G26" s="11"/>
       <c r="H26" s="12"/>
@@ -1721,13 +1614,13 @@
         <v>27</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G27" s="11"/>
       <c r="H27" s="12"/>
@@ -1744,13 +1637,13 @@
         <v>27</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G28" s="11"/>
       <c r="H28" s="12"/>
@@ -1767,13 +1660,13 @@
         <v>27</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G29" s="11"/>
       <c r="H29" s="12"/>
@@ -1790,13 +1683,13 @@
         <v>27</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G30" s="11"/>
       <c r="H30" s="12"/>
@@ -1813,13 +1706,13 @@
         <v>27</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G31" s="11"/>
       <c r="H31" s="12"/>
@@ -1836,13 +1729,13 @@
         <v>55</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>63</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G32" s="11"/>
       <c r="H32" s="12"/>
@@ -1859,13 +1752,13 @@
         <v>55</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>63</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G33" s="11"/>
       <c r="H33" s="12"/>
@@ -1882,13 +1775,13 @@
         <v>27</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>38</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G34" s="11"/>
       <c r="H34" s="12"/>
@@ -1905,13 +1798,13 @@
         <v>55</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>63</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G35" s="11"/>
       <c r="H35" s="12"/>
@@ -1928,13 +1821,13 @@
         <v>55</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>63</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G36" s="11"/>
       <c r="H36" s="12"/>
@@ -1951,13 +1844,13 @@
         <v>55</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>63</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G37" s="11"/>
       <c r="H37" s="12"/>
@@ -1987,13 +1880,13 @@
         <v>27</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G39" s="11"/>
       <c r="H39" s="12"/>
@@ -2010,13 +1903,13 @@
         <v>55</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="E40" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G40" s="11"/>
       <c r="H40" s="12"/>
@@ -2033,13 +1926,13 @@
         <v>27</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G41" s="11"/>
       <c r="H41" s="12"/>
@@ -2056,13 +1949,13 @@
         <v>104</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="E42" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G42" s="11"/>
       <c r="H42" s="12"/>
@@ -2079,13 +1972,13 @@
         <v>58</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G43" s="11"/>
       <c r="H43" s="12"/>
@@ -2102,13 +1995,13 @@
         <v>55</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="E44" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G44" s="11"/>
       <c r="H44" s="12"/>
@@ -2125,13 +2018,13 @@
         <v>27</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>35</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G45" s="11"/>
       <c r="H45" s="12"/>
@@ -2148,13 +2041,13 @@
         <v>27</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="E46" s="9" t="s">
         <v>35</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G46" s="11"/>
       <c r="H46" s="12"/>
@@ -2171,13 +2064,13 @@
         <v>27</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>63</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G47" s="11"/>
       <c r="H47" s="12"/>
@@ -2185,7 +2078,7 @@
     </row>
     <row r="48" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
@@ -2196,222 +2089,28 @@
       <c r="H48" s="18"/>
       <c r="I48" s="18"/>
     </row>
-    <row r="49" spans="1:9" s="25" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" s="23" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A49" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="B49" s="24" t="s">
-        <v>192</v>
-      </c>
-      <c r="C49" s="23"/>
-      <c r="D49" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="E49" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="F49" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="G49" s="24" t="s">
-        <v>195</v>
-      </c>
-      <c r="H49" s="24"/>
-      <c r="I49" s="24"/>
-    </row>
-    <row r="50" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="B50" s="15"/>
-      <c r="C50" s="15"/>
-      <c r="D50" s="15"/>
-      <c r="E50" s="15"/>
-      <c r="F50" s="16"/>
-      <c r="G50" s="17"/>
-      <c r="H50" s="18"/>
-      <c r="I50" s="18"/>
-    </row>
-    <row r="51" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A51" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="E51" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F51" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="G51" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="H51" s="12"/>
-      <c r="I51" s="20" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="B52" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="E52" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="F52" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="G52" s="21"/>
-      <c r="H52" s="12"/>
-      <c r="I52" s="22"/>
-    </row>
-    <row r="53" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A53" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="B53" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="C53" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="E53" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F53" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="G53" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="H53" s="12"/>
-      <c r="I53" s="20" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A54" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="B54" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="C54" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="E54" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="F54" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="G54" s="21"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="22"/>
-    </row>
-    <row r="55" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="B55" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="C55" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D55" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="E55" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="F55" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="G55" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="H55" s="12"/>
-      <c r="I55" s="20" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A56" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="B56" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="C56" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D56" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E56" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F56" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="G56" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="H56" s="12"/>
-      <c r="I56" s="20" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A57" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="B57" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="C57" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D57" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="E57" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F57" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="G57" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="H57" s="12"/>
-      <c r="I57" s="20" t="s">
-        <v>189</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="B49" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="C49" s="21"/>
+      <c r="D49" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="E49" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="F49" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="G49" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="H49" s="22"/>
+      <c r="I49" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Docs/QA-Testing/Test_Case_Report_API.xlsx
+++ b/Docs/QA-Testing/Test_Case_Report_API.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20398"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\Online-Store-sprint-4 (1)\Online-Store-sprint-4\Docs\QA-Testing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KiemChungPhanMem\Docs\QA-Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68816755-4B48-4825-B38F-72ACC9445B5E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{548BBB32-1E44-476F-8B29-4D87FE1D1492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="165">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -582,7 +582,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -604,6 +604,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9D9D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -662,9 +674,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -685,9 +694,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -700,8 +706,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1012,20 +1024,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A99EB60-1787-4B02-8F08-DF5C4102B1D2}">
   <dimension ref="A1:I49"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.88671875" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1" outlineLevel="1"/>
     <col min="4" max="4" width="24" customWidth="1" outlineLevel="1"/>
-    <col min="5" max="5" width="22.28515625" customWidth="1" outlineLevel="1"/>
-    <col min="6" max="6" width="19.5703125" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="6" customWidth="1"/>
-    <col min="8" max="8" width="13.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" customWidth="1" outlineLevel="1"/>
+    <col min="6" max="6" width="19.5546875" customWidth="1"/>
+    <col min="7" max="7" width="14.88671875" style="6" customWidth="1"/>
+    <col min="8" max="8" width="13.5546875" customWidth="1"/>
     <col min="9" max="9" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1054,7 +1066,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -1067,7 +1079,7 @@
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
     </row>
-    <row r="3" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>7</v>
       </c>
@@ -1083,14 +1095,16 @@
       <c r="E3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-    </row>
-    <row r="4" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="F3" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I3" s="11"/>
+    </row>
+    <row r="4" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>11</v>
       </c>
@@ -1106,14 +1120,16 @@
       <c r="E4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G4" s="11"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-    </row>
-    <row r="5" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="F4" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G4" s="10"/>
+      <c r="H4" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I4" s="11"/>
+    </row>
+    <row r="5" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>12</v>
       </c>
@@ -1129,14 +1145,16 @@
       <c r="E5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G5" s="11"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-    </row>
-    <row r="6" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="F5" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G5" s="10"/>
+      <c r="H5" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I5" s="11"/>
+    </row>
+    <row r="6" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>15</v>
       </c>
@@ -1152,14 +1170,16 @@
       <c r="E6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G6" s="11"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-    </row>
-    <row r="7" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="F6" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I6" s="11"/>
+    </row>
+    <row r="7" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>18</v>
       </c>
@@ -1175,14 +1195,16 @@
       <c r="E7" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G7" s="11"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-    </row>
-    <row r="8" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="F7" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G7" s="10"/>
+      <c r="H7" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I7" s="11"/>
+    </row>
+    <row r="8" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>21</v>
       </c>
@@ -1198,14 +1220,16 @@
       <c r="E8" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G8" s="11"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-    </row>
-    <row r="9" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="F8" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G8" s="10"/>
+      <c r="H8" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I8" s="11"/>
+    </row>
+    <row r="9" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>25</v>
       </c>
@@ -1221,14 +1245,16 @@
       <c r="E9" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G9" s="11"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-    </row>
-    <row r="10" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F9" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G9" s="10"/>
+      <c r="H9" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I9" s="11"/>
+    </row>
+    <row r="10" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>29</v>
       </c>
@@ -1244,14 +1270,16 @@
       <c r="E10" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F10" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G10" s="11"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-    </row>
-    <row r="11" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="F10" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G10" s="10"/>
+      <c r="H10" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I10" s="11"/>
+    </row>
+    <row r="11" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
         <v>32</v>
       </c>
@@ -1267,14 +1295,16 @@
       <c r="E11" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G11" s="11"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-    </row>
-    <row r="12" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F11" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G11" s="10"/>
+      <c r="H11" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I11" s="11"/>
+    </row>
+    <row r="12" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>36</v>
       </c>
@@ -1290,14 +1320,16 @@
       <c r="E12" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G12" s="11"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-    </row>
-    <row r="13" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="F12" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G12" s="10"/>
+      <c r="H12" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I12" s="11"/>
+    </row>
+    <row r="13" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
         <v>39</v>
       </c>
@@ -1313,27 +1345,29 @@
       <c r="E13" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G13" s="11"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="13"/>
-    </row>
-    <row r="14" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
+      <c r="F13" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G13" s="10"/>
+      <c r="H13" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I13" s="12"/>
+    </row>
+    <row r="14" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-    </row>
-    <row r="15" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+    </row>
+    <row r="15" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
         <v>45</v>
       </c>
@@ -1349,14 +1383,16 @@
       <c r="E15" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G15" s="11"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-    </row>
-    <row r="16" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F15" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G15" s="10"/>
+      <c r="H15" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I15" s="11"/>
+    </row>
+    <row r="16" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
         <v>48</v>
       </c>
@@ -1372,14 +1408,16 @@
       <c r="E16" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F16" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G16" s="11"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-    </row>
-    <row r="17" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="F16" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G16" s="10"/>
+      <c r="H16" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I16" s="11"/>
+    </row>
+    <row r="17" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
         <v>51</v>
       </c>
@@ -1395,14 +1433,16 @@
       <c r="E17" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G17" s="11"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-    </row>
-    <row r="18" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="F17" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G17" s="10"/>
+      <c r="H17" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I17" s="11"/>
+    </row>
+    <row r="18" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>53</v>
       </c>
@@ -1418,14 +1458,16 @@
       <c r="E18" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F18" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G18" s="11"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-    </row>
-    <row r="19" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="F18" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G18" s="10"/>
+      <c r="H18" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I18" s="11"/>
+    </row>
+    <row r="19" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
         <v>56</v>
       </c>
@@ -1441,14 +1483,16 @@
       <c r="E19" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F19" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G19" s="11"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-    </row>
-    <row r="20" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="F19" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G19" s="10"/>
+      <c r="H19" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I19" s="11"/>
+    </row>
+    <row r="20" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>59</v>
       </c>
@@ -1464,14 +1508,16 @@
       <c r="E20" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F20" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G20" s="11"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-    </row>
-    <row r="21" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="F20" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G20" s="10"/>
+      <c r="H20" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I20" s="11"/>
+    </row>
+    <row r="21" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
         <v>61</v>
       </c>
@@ -1487,14 +1533,16 @@
       <c r="E21" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F21" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G21" s="11"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-    </row>
-    <row r="22" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="F21" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G21" s="10"/>
+      <c r="H21" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I21" s="11"/>
+    </row>
+    <row r="22" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>64</v>
       </c>
@@ -1510,18 +1558,20 @@
       <c r="E22" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F22" s="19" t="s">
+      <c r="F22" s="24" t="s">
         <v>155</v>
       </c>
-      <c r="G22" s="11" t="s">
+      <c r="G22" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="H22" s="12"/>
-      <c r="I22" s="20" t="s">
+      <c r="H22" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I22" s="18" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
         <v>66</v>
       </c>
@@ -1537,14 +1587,16 @@
       <c r="E23" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G23" s="11"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-    </row>
-    <row r="24" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="F23" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G23" s="10"/>
+      <c r="H23" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I23" s="11"/>
+    </row>
+    <row r="24" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>68</v>
       </c>
@@ -1560,27 +1612,29 @@
       <c r="E24" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F24" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G24" s="11"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-    </row>
-    <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
+      <c r="F24" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G24" s="10"/>
+      <c r="H24" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I24" s="11"/>
+    </row>
+    <row r="25" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
-    </row>
-    <row r="26" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+    </row>
+    <row r="26" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>71</v>
       </c>
@@ -1596,14 +1650,16 @@
       <c r="E26" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F26" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G26" s="11"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
-    </row>
-    <row r="27" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F26" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G26" s="10"/>
+      <c r="H26" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I26" s="11"/>
+    </row>
+    <row r="27" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
         <v>73</v>
       </c>
@@ -1619,14 +1675,16 @@
       <c r="E27" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F27" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G27" s="11"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-    </row>
-    <row r="28" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F27" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G27" s="10"/>
+      <c r="H27" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I27" s="11"/>
+    </row>
+    <row r="28" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>75</v>
       </c>
@@ -1642,14 +1700,16 @@
       <c r="E28" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F28" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G28" s="11"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-    </row>
-    <row r="29" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F28" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G28" s="10"/>
+      <c r="H28" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I28" s="11"/>
+    </row>
+    <row r="29" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
         <v>77</v>
       </c>
@@ -1665,14 +1725,16 @@
       <c r="E29" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F29" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G29" s="11"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-    </row>
-    <row r="30" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F29" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G29" s="10"/>
+      <c r="H29" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I29" s="11"/>
+    </row>
+    <row r="30" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>79</v>
       </c>
@@ -1688,14 +1750,16 @@
       <c r="E30" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F30" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G30" s="11"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-    </row>
-    <row r="31" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F30" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G30" s="10"/>
+      <c r="H30" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I30" s="11"/>
+    </row>
+    <row r="31" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
         <v>81</v>
       </c>
@@ -1711,14 +1775,16 @@
       <c r="E31" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F31" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G31" s="11"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-    </row>
-    <row r="32" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F31" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G31" s="10"/>
+      <c r="H31" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I31" s="11"/>
+    </row>
+    <row r="32" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>83</v>
       </c>
@@ -1734,14 +1800,16 @@
       <c r="E32" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F32" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G32" s="11"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-    </row>
-    <row r="33" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F32" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G32" s="10"/>
+      <c r="H32" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I32" s="11"/>
+    </row>
+    <row r="33" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
         <v>85</v>
       </c>
@@ -1757,14 +1825,16 @@
       <c r="E33" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G33" s="11"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-    </row>
-    <row r="34" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="F33" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G33" s="10"/>
+      <c r="H33" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I33" s="11"/>
+    </row>
+    <row r="34" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>87</v>
       </c>
@@ -1780,14 +1850,16 @@
       <c r="E34" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F34" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G34" s="11"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
-    </row>
-    <row r="35" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F34" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G34" s="10"/>
+      <c r="H34" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I34" s="11"/>
+    </row>
+    <row r="35" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
         <v>89</v>
       </c>
@@ -1803,14 +1875,16 @@
       <c r="E35" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F35" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G35" s="11"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="12"/>
-    </row>
-    <row r="36" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F35" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G35" s="10"/>
+      <c r="H35" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I35" s="11"/>
+    </row>
+    <row r="36" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>91</v>
       </c>
@@ -1826,14 +1900,16 @@
       <c r="E36" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F36" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G36" s="11"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="12"/>
-    </row>
-    <row r="37" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F36" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G36" s="10"/>
+      <c r="H36" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I36" s="11"/>
+    </row>
+    <row r="37" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A37" s="9" t="s">
         <v>93</v>
       </c>
@@ -1849,27 +1925,29 @@
       <c r="E37" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F37" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G37" s="11"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="12"/>
-    </row>
-    <row r="38" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
+      <c r="F37" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G37" s="10"/>
+      <c r="H37" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I37" s="11"/>
+    </row>
+    <row r="38" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
-    </row>
-    <row r="39" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+    </row>
+    <row r="39" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
         <v>96</v>
       </c>
@@ -1885,14 +1963,16 @@
       <c r="E39" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G39" s="11"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="12"/>
-    </row>
-    <row r="40" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F39" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G39" s="10"/>
+      <c r="H39" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I39" s="11"/>
+    </row>
+    <row r="40" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
         <v>98</v>
       </c>
@@ -1908,14 +1988,16 @@
       <c r="E40" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F40" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G40" s="11"/>
-      <c r="H40" s="12"/>
-      <c r="I40" s="12"/>
-    </row>
-    <row r="41" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F40" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G40" s="10"/>
+      <c r="H40" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I40" s="11"/>
+    </row>
+    <row r="41" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
         <v>100</v>
       </c>
@@ -1931,14 +2013,16 @@
       <c r="E41" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F41" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G41" s="11"/>
-      <c r="H41" s="12"/>
-      <c r="I41" s="12"/>
-    </row>
-    <row r="42" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F41" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G41" s="10"/>
+      <c r="H41" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I41" s="11"/>
+    </row>
+    <row r="42" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
         <v>102</v>
       </c>
@@ -1954,14 +2038,16 @@
       <c r="E42" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F42" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G42" s="11"/>
-      <c r="H42" s="12"/>
-      <c r="I42" s="13"/>
-    </row>
-    <row r="43" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F42" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G42" s="10"/>
+      <c r="H42" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I42" s="12"/>
+    </row>
+    <row r="43" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
         <v>105</v>
       </c>
@@ -1977,14 +2063,16 @@
       <c r="E43" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G43" s="11"/>
-      <c r="H43" s="12"/>
-      <c r="I43" s="13"/>
-    </row>
-    <row r="44" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F43" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G43" s="10"/>
+      <c r="H43" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I43" s="12"/>
+    </row>
+    <row r="44" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>107</v>
       </c>
@@ -2000,14 +2088,16 @@
       <c r="E44" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F44" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G44" s="11"/>
-      <c r="H44" s="12"/>
-      <c r="I44" s="13"/>
-    </row>
-    <row r="45" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F44" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G44" s="10"/>
+      <c r="H44" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I44" s="12"/>
+    </row>
+    <row r="45" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
         <v>109</v>
       </c>
@@ -2023,14 +2113,16 @@
       <c r="E45" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F45" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G45" s="11"/>
-      <c r="H45" s="12"/>
-      <c r="I45" s="12"/>
-    </row>
-    <row r="46" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="F45" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G45" s="10"/>
+      <c r="H45" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I45" s="11"/>
+    </row>
+    <row r="46" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>111</v>
       </c>
@@ -2046,14 +2138,16 @@
       <c r="E46" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F46" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G46" s="11"/>
-      <c r="H46" s="12"/>
-      <c r="I46" s="12"/>
-    </row>
-    <row r="47" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="F46" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G46" s="10"/>
+      <c r="H46" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I46" s="11"/>
+    </row>
+    <row r="47" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
         <v>113</v>
       </c>
@@ -2069,48 +2163,52 @@
       <c r="E47" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="G47" s="11"/>
-      <c r="H47" s="12"/>
-      <c r="I47" s="12"/>
-    </row>
-    <row r="48" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="14" t="s">
+      <c r="F47" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="G47" s="10"/>
+      <c r="H47" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I47" s="11"/>
+    </row>
+    <row r="48" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="B48" s="15"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="15"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="17"/>
-      <c r="H48" s="18"/>
-      <c r="I48" s="18"/>
-    </row>
-    <row r="49" spans="1:9" s="23" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="B48" s="14"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="16"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="17"/>
+    </row>
+    <row r="49" spans="1:9" s="21" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A49" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="B49" s="22" t="s">
+      <c r="B49" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="C49" s="21"/>
-      <c r="D49" s="22" t="s">
+      <c r="C49" s="19"/>
+      <c r="D49" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="E49" s="22" t="s">
+      <c r="E49" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="F49" s="24" t="s">
+      <c r="F49" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="G49" s="22" t="s">
+      <c r="G49" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="H49" s="22"/>
-      <c r="I49" s="22"/>
+      <c r="H49" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I49" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Docs/QA-Testing/Test_Case_Report_API.xlsx
+++ b/Docs/QA-Testing/Test_Case_Report_API.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KiemChungPhanMem\Docs\QA-Testing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Downloads/Online-Store/Docs/QA-Testing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{548BBB32-1E44-476F-8B29-4D87FE1D1492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{434FEF45-7D5E-0B4A-AD52-F2630913D8C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -582,7 +582,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -604,18 +604,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9D9D9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -674,6 +662,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -694,6 +685,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -706,14 +700,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1024,20 +1012,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A99EB60-1787-4B02-8F08-DF5C4102B1D2}">
   <dimension ref="A1:I49"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.88671875" customWidth="1"/>
+    <col min="1" max="1" width="23.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.6640625" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1" outlineLevel="1"/>
     <col min="4" max="4" width="24" customWidth="1" outlineLevel="1"/>
     <col min="5" max="5" width="22.33203125" customWidth="1" outlineLevel="1"/>
-    <col min="6" max="6" width="19.5546875" customWidth="1"/>
-    <col min="7" max="7" width="14.88671875" style="6" customWidth="1"/>
-    <col min="8" max="8" width="13.5546875" customWidth="1"/>
+    <col min="6" max="6" width="19.5" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" style="6" customWidth="1"/>
+    <col min="8" max="8" width="13.5" customWidth="1"/>
     <col min="9" max="9" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1066,7 +1054,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="18" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -1079,7 +1067,7 @@
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
     </row>
-    <row r="3" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
         <v>7</v>
       </c>
@@ -1095,16 +1083,16 @@
       <c r="E3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I3" s="11"/>
-    </row>
-    <row r="4" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="F3" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G3" s="11"/>
+      <c r="H3" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I3" s="12"/>
+    </row>
+    <row r="4" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>11</v>
       </c>
@@ -1120,16 +1108,16 @@
       <c r="E4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I4" s="11"/>
-    </row>
-    <row r="5" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="F4" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G4" s="11"/>
+      <c r="H4" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I4" s="12"/>
+    </row>
+    <row r="5" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
         <v>12</v>
       </c>
@@ -1145,16 +1133,16 @@
       <c r="E5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I5" s="11"/>
-    </row>
-    <row r="6" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="F5" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G5" s="11"/>
+      <c r="H5" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I5" s="12"/>
+    </row>
+    <row r="6" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
         <v>15</v>
       </c>
@@ -1170,16 +1158,16 @@
       <c r="E6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I6" s="11"/>
-    </row>
-    <row r="7" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="F6" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G6" s="11"/>
+      <c r="H6" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I6" s="12"/>
+    </row>
+    <row r="7" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
         <v>18</v>
       </c>
@@ -1195,16 +1183,16 @@
       <c r="E7" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G7" s="10"/>
-      <c r="H7" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I7" s="11"/>
-    </row>
-    <row r="8" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="F7" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G7" s="11"/>
+      <c r="H7" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I7" s="12"/>
+    </row>
+    <row r="8" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
         <v>21</v>
       </c>
@@ -1220,16 +1208,16 @@
       <c r="E8" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I8" s="11"/>
-    </row>
-    <row r="9" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="F8" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G8" s="11"/>
+      <c r="H8" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I8" s="12"/>
+    </row>
+    <row r="9" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
         <v>25</v>
       </c>
@@ -1245,16 +1233,16 @@
       <c r="E9" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G9" s="10"/>
-      <c r="H9" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I9" s="11"/>
-    </row>
-    <row r="10" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="F9" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G9" s="11"/>
+      <c r="H9" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I9" s="12"/>
+    </row>
+    <row r="10" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
         <v>29</v>
       </c>
@@ -1270,16 +1258,16 @@
       <c r="E10" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F10" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I10" s="11"/>
-    </row>
-    <row r="11" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="F10" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G10" s="11"/>
+      <c r="H10" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I10" s="12"/>
+    </row>
+    <row r="11" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
         <v>32</v>
       </c>
@@ -1295,16 +1283,16 @@
       <c r="E11" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I11" s="11"/>
-    </row>
-    <row r="12" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="F11" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G11" s="11"/>
+      <c r="H11" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I11" s="12"/>
+    </row>
+    <row r="12" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
         <v>36</v>
       </c>
@@ -1320,16 +1308,16 @@
       <c r="E12" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G12" s="10"/>
-      <c r="H12" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I12" s="11"/>
-    </row>
-    <row r="13" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="F12" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G12" s="11"/>
+      <c r="H12" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I12" s="12"/>
+    </row>
+    <row r="13" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
         <v>39</v>
       </c>
@@ -1345,29 +1333,29 @@
       <c r="E13" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G13" s="10"/>
-      <c r="H13" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I13" s="12"/>
-    </row>
-    <row r="14" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="13" t="s">
+      <c r="F13" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G13" s="11"/>
+      <c r="H13" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I13" s="13"/>
+    </row>
+    <row r="14" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A14" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-    </row>
-    <row r="15" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+    </row>
+    <row r="15" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
         <v>45</v>
       </c>
@@ -1383,16 +1371,16 @@
       <c r="E15" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G15" s="10"/>
-      <c r="H15" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I15" s="11"/>
-    </row>
-    <row r="16" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="F15" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G15" s="11"/>
+      <c r="H15" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I15" s="12"/>
+    </row>
+    <row r="16" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
         <v>48</v>
       </c>
@@ -1408,16 +1396,16 @@
       <c r="E16" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F16" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G16" s="10"/>
-      <c r="H16" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I16" s="11"/>
-    </row>
-    <row r="17" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="F16" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G16" s="11"/>
+      <c r="H16" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I16" s="12"/>
+    </row>
+    <row r="17" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
         <v>51</v>
       </c>
@@ -1433,16 +1421,16 @@
       <c r="E17" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G17" s="10"/>
-      <c r="H17" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I17" s="11"/>
-    </row>
-    <row r="18" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="F17" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G17" s="11"/>
+      <c r="H17" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I17" s="12"/>
+    </row>
+    <row r="18" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
         <v>53</v>
       </c>
@@ -1458,16 +1446,16 @@
       <c r="E18" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F18" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I18" s="11"/>
-    </row>
-    <row r="19" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="F18" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G18" s="11"/>
+      <c r="H18" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I18" s="12"/>
+    </row>
+    <row r="19" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
         <v>56</v>
       </c>
@@ -1483,16 +1471,16 @@
       <c r="E19" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F19" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G19" s="10"/>
-      <c r="H19" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I19" s="11"/>
-    </row>
-    <row r="20" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="F19" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G19" s="11"/>
+      <c r="H19" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I19" s="12"/>
+    </row>
+    <row r="20" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
         <v>59</v>
       </c>
@@ -1508,16 +1496,16 @@
       <c r="E20" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F20" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G20" s="10"/>
-      <c r="H20" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I20" s="11"/>
-    </row>
-    <row r="21" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="F20" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G20" s="11"/>
+      <c r="H20" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I20" s="12"/>
+    </row>
+    <row r="21" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
         <v>61</v>
       </c>
@@ -1533,16 +1521,16 @@
       <c r="E21" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F21" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G21" s="10"/>
-      <c r="H21" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I21" s="11"/>
-    </row>
-    <row r="22" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="F21" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G21" s="11"/>
+      <c r="H21" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I21" s="12"/>
+    </row>
+    <row r="22" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
         <v>64</v>
       </c>
@@ -1558,20 +1546,20 @@
       <c r="E22" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F22" s="24" t="s">
+      <c r="F22" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="G22" s="10" t="s">
+      <c r="G22" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="H22" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I22" s="18" t="s">
+      <c r="H22" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I22" s="20" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
         <v>66</v>
       </c>
@@ -1587,16 +1575,16 @@
       <c r="E23" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F23" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G23" s="10"/>
-      <c r="H23" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I23" s="11"/>
-    </row>
-    <row r="24" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="F23" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G23" s="11"/>
+      <c r="H23" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I23" s="12"/>
+    </row>
+    <row r="24" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
         <v>68</v>
       </c>
@@ -1612,29 +1600,29 @@
       <c r="E24" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F24" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G24" s="10"/>
-      <c r="H24" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I24" s="11"/>
-    </row>
-    <row r="25" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="13" t="s">
+      <c r="F24" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G24" s="11"/>
+      <c r="H24" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I24" s="12"/>
+    </row>
+    <row r="25" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A25" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-    </row>
-    <row r="26" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+    </row>
+    <row r="26" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
         <v>71</v>
       </c>
@@ -1650,16 +1638,16 @@
       <c r="E26" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F26" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G26" s="10"/>
-      <c r="H26" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I26" s="11"/>
-    </row>
-    <row r="27" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="F26" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G26" s="11"/>
+      <c r="H26" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I26" s="12"/>
+    </row>
+    <row r="27" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
         <v>73</v>
       </c>
@@ -1675,16 +1663,16 @@
       <c r="E27" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F27" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G27" s="10"/>
-      <c r="H27" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I27" s="11"/>
-    </row>
-    <row r="28" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="F27" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G27" s="11"/>
+      <c r="H27" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I27" s="12"/>
+    </row>
+    <row r="28" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
         <v>75</v>
       </c>
@@ -1700,16 +1688,16 @@
       <c r="E28" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F28" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G28" s="10"/>
-      <c r="H28" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I28" s="11"/>
-    </row>
-    <row r="29" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="F28" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G28" s="11"/>
+      <c r="H28" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I28" s="12"/>
+    </row>
+    <row r="29" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
         <v>77</v>
       </c>
@@ -1725,16 +1713,16 @@
       <c r="E29" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F29" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G29" s="10"/>
-      <c r="H29" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I29" s="11"/>
-    </row>
-    <row r="30" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="F29" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G29" s="11"/>
+      <c r="H29" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I29" s="12"/>
+    </row>
+    <row r="30" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A30" s="9" t="s">
         <v>79</v>
       </c>
@@ -1750,16 +1738,16 @@
       <c r="E30" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F30" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G30" s="10"/>
-      <c r="H30" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I30" s="11"/>
-    </row>
-    <row r="31" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="F30" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G30" s="11"/>
+      <c r="H30" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I30" s="12"/>
+    </row>
+    <row r="31" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A31" s="9" t="s">
         <v>81</v>
       </c>
@@ -1775,16 +1763,16 @@
       <c r="E31" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F31" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G31" s="10"/>
-      <c r="H31" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I31" s="11"/>
-    </row>
-    <row r="32" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="F31" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G31" s="11"/>
+      <c r="H31" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I31" s="12"/>
+    </row>
+    <row r="32" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A32" s="9" t="s">
         <v>83</v>
       </c>
@@ -1800,16 +1788,16 @@
       <c r="E32" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F32" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G32" s="10"/>
-      <c r="H32" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I32" s="11"/>
-    </row>
-    <row r="33" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="F32" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G32" s="11"/>
+      <c r="H32" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I32" s="12"/>
+    </row>
+    <row r="33" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A33" s="9" t="s">
         <v>85</v>
       </c>
@@ -1825,16 +1813,16 @@
       <c r="E33" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F33" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G33" s="10"/>
-      <c r="H33" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I33" s="11"/>
-    </row>
-    <row r="34" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="F33" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G33" s="11"/>
+      <c r="H33" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I33" s="12"/>
+    </row>
+    <row r="34" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A34" s="9" t="s">
         <v>87</v>
       </c>
@@ -1850,16 +1838,16 @@
       <c r="E34" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F34" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G34" s="10"/>
-      <c r="H34" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I34" s="11"/>
-    </row>
-    <row r="35" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="F34" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G34" s="11"/>
+      <c r="H34" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I34" s="12"/>
+    </row>
+    <row r="35" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A35" s="9" t="s">
         <v>89</v>
       </c>
@@ -1875,16 +1863,16 @@
       <c r="E35" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F35" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G35" s="10"/>
-      <c r="H35" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I35" s="11"/>
-    </row>
-    <row r="36" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="F35" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G35" s="11"/>
+      <c r="H35" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I35" s="12"/>
+    </row>
+    <row r="36" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A36" s="9" t="s">
         <v>91</v>
       </c>
@@ -1900,16 +1888,16 @@
       <c r="E36" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F36" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G36" s="10"/>
-      <c r="H36" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I36" s="11"/>
-    </row>
-    <row r="37" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="F36" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G36" s="11"/>
+      <c r="H36" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I36" s="12"/>
+    </row>
+    <row r="37" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A37" s="9" t="s">
         <v>93</v>
       </c>
@@ -1925,29 +1913,29 @@
       <c r="E37" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F37" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G37" s="10"/>
-      <c r="H37" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I37" s="11"/>
-    </row>
-    <row r="38" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="13" t="s">
+      <c r="F37" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G37" s="11"/>
+      <c r="H37" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I37" s="12"/>
+    </row>
+    <row r="38" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A38" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="17"/>
-    </row>
-    <row r="39" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B38" s="15"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
+    </row>
+    <row r="39" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A39" s="9" t="s">
         <v>96</v>
       </c>
@@ -1963,16 +1951,16 @@
       <c r="E39" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F39" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G39" s="10"/>
-      <c r="H39" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I39" s="11"/>
-    </row>
-    <row r="40" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="F39" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G39" s="11"/>
+      <c r="H39" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I39" s="12"/>
+    </row>
+    <row r="40" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A40" s="9" t="s">
         <v>98</v>
       </c>
@@ -1988,16 +1976,16 @@
       <c r="E40" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F40" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G40" s="10"/>
-      <c r="H40" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I40" s="11"/>
-    </row>
-    <row r="41" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="F40" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G40" s="11"/>
+      <c r="H40" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I40" s="12"/>
+    </row>
+    <row r="41" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A41" s="9" t="s">
         <v>100</v>
       </c>
@@ -2013,16 +2001,16 @@
       <c r="E41" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F41" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G41" s="10"/>
-      <c r="H41" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I41" s="11"/>
-    </row>
-    <row r="42" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="F41" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G41" s="11"/>
+      <c r="H41" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I41" s="12"/>
+    </row>
+    <row r="42" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A42" s="9" t="s">
         <v>102</v>
       </c>
@@ -2038,16 +2026,16 @@
       <c r="E42" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F42" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G42" s="10"/>
-      <c r="H42" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I42" s="12"/>
-    </row>
-    <row r="43" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="F42" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G42" s="11"/>
+      <c r="H42" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I42" s="13"/>
+    </row>
+    <row r="43" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A43" s="9" t="s">
         <v>105</v>
       </c>
@@ -2063,16 +2051,16 @@
       <c r="E43" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F43" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G43" s="10"/>
-      <c r="H43" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I43" s="12"/>
-    </row>
-    <row r="44" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="F43" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G43" s="11"/>
+      <c r="H43" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I43" s="13"/>
+    </row>
+    <row r="44" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A44" s="9" t="s">
         <v>107</v>
       </c>
@@ -2088,16 +2076,16 @@
       <c r="E44" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F44" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G44" s="10"/>
-      <c r="H44" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I44" s="12"/>
-    </row>
-    <row r="45" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="F44" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G44" s="11"/>
+      <c r="H44" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I44" s="13"/>
+    </row>
+    <row r="45" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A45" s="9" t="s">
         <v>109</v>
       </c>
@@ -2113,16 +2101,16 @@
       <c r="E45" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F45" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G45" s="10"/>
-      <c r="H45" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I45" s="11"/>
-    </row>
-    <row r="46" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="F45" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G45" s="11"/>
+      <c r="H45" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I45" s="12"/>
+    </row>
+    <row r="46" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A46" s="9" t="s">
         <v>111</v>
       </c>
@@ -2138,16 +2126,16 @@
       <c r="E46" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F46" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G46" s="10"/>
-      <c r="H46" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I46" s="11"/>
-    </row>
-    <row r="47" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="F46" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G46" s="11"/>
+      <c r="H46" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I46" s="12"/>
+    </row>
+    <row r="47" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A47" s="9" t="s">
         <v>113</v>
       </c>
@@ -2163,52 +2151,52 @@
       <c r="E47" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F47" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G47" s="10"/>
-      <c r="H47" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I47" s="11"/>
-    </row>
-    <row r="48" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="13" t="s">
+      <c r="F47" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G47" s="11"/>
+      <c r="H47" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I47" s="12"/>
+    </row>
+    <row r="48" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A48" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="16"/>
-      <c r="H48" s="17"/>
-      <c r="I48" s="17"/>
-    </row>
-    <row r="49" spans="1:9" s="21" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="B48" s="15"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="18"/>
+      <c r="I48" s="18"/>
+    </row>
+    <row r="49" spans="1:9" s="23" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A49" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="B49" s="20" t="s">
+      <c r="B49" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="C49" s="19"/>
-      <c r="D49" s="20" t="s">
+      <c r="C49" s="21"/>
+      <c r="D49" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="E49" s="20" t="s">
+      <c r="E49" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="F49" s="23" t="s">
+      <c r="F49" s="24" t="s">
         <v>155</v>
       </c>
-      <c r="G49" s="20" t="s">
+      <c r="G49" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="H49" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="I49" s="20"/>
+      <c r="H49" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I49" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
